--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\Documents\УЧЕБА\System Design 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B704A4B5-BD80-4A01-B8FC-D0F8A75674D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B61FAD8-642F-4A96-8C32-8A6DFF8B4602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>

--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\Documents\УЧЕБА\System Design 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B61FAD8-642F-4A96-8C32-8A6DFF8B4602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D390C9-1FED-4E47-B525-D8E08FE5F78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="256">
   <si>
     <t>Клиенты и точки входа</t>
   </si>
@@ -1183,6 +1183,9 @@
   </si>
   <si>
     <t>Distributed Lock Manager (DLM)</t>
+  </si>
+  <si>
+    <t>БД реестра схем</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC358B7-DB9E-4D8A-87B3-F1C518B618F4}">
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -2269,450 +2272,456 @@
         <v>222</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="18">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:7">
+      <c r="A41" s="3"/>
+      <c r="B41" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="18">
+      <c r="A42" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-    </row>
-    <row r="42" spans="1:7" ht="150">
-      <c r="A42" s="3"/>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:7" ht="150">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D43" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F43" s="11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25.5">
-      <c r="B43" s="4" t="s">
+    <row r="44" spans="1:7" ht="25.5">
+      <c r="B44" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F44" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="60">
-      <c r="A44" s="3"/>
-      <c r="B44" s="13" t="s">
+    <row r="45" spans="1:7" ht="60">
+      <c r="A45" s="3"/>
+      <c r="B45" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C45" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14" t="s">
+      <c r="D45" s="14"/>
+      <c r="E45" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F45" s="14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18">
-      <c r="A45" s="16" t="s">
+    <row r="46" spans="1:7" ht="18">
+      <c r="A46" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-    </row>
-    <row r="46" spans="1:7" ht="75">
-      <c r="A46" s="3"/>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="17"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" ht="75">
+      <c r="A47" s="3"/>
+      <c r="B47" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C47" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F47" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" ht="30">
-      <c r="A47" s="3"/>
-      <c r="B47" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>143</v>
-      </c>
+      <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7" ht="30">
       <c r="A48" s="3"/>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30">
+      <c r="A49" s="3"/>
+      <c r="B49" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C49" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F49" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18">
-      <c r="A49" s="16" t="s">
+    <row r="50" spans="1:7" ht="18">
+      <c r="A50" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-    </row>
-    <row r="50" spans="1:7" ht="30">
-      <c r="A50" s="3"/>
-      <c r="B50" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="375">
+      <c r="B50" s="17"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+    </row>
+    <row r="51" spans="1:7" ht="30">
       <c r="A51" s="3"/>
       <c r="B51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="375">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F52" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="10"/>
-    </row>
-    <row r="52" spans="1:7" ht="18">
-      <c r="A52" s="16" t="s">
+      <c r="G52" s="10"/>
+    </row>
+    <row r="53" spans="1:7" ht="18">
+      <c r="A53" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-    </row>
-    <row r="53" spans="1:7" ht="30">
-      <c r="A53" s="3"/>
-      <c r="B53" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>163</v>
-      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
     </row>
     <row r="54" spans="1:7" ht="30">
       <c r="A54" s="3"/>
       <c r="B54" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="30">
       <c r="A55" s="3"/>
       <c r="B55" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="30">
       <c r="A56" s="3"/>
       <c r="B56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="75">
+      <c r="A57" s="3"/>
+      <c r="B57" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F57" s="11" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18">
-      <c r="A57" s="16" t="s">
+    <row r="58" spans="1:7" ht="18">
+      <c r="A58" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-    </row>
-    <row r="58" spans="1:7" ht="45">
-      <c r="A58" s="3"/>
-      <c r="B58" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="60">
+      <c r="B58" s="17"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+    </row>
+    <row r="59" spans="1:7" ht="45">
       <c r="A59" s="3"/>
       <c r="B59" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="30">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="60">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="30">
       <c r="A61" s="3"/>
       <c r="B61" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="300">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="30">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="60">
+        <v>146</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="300">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="60">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="45">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C65" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F65" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="18">
-      <c r="A65" s="16" t="s">
+    <row r="66" spans="1:6" ht="18">
+      <c r="A66" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-    </row>
-    <row r="66" spans="1:6" ht="30">
-      <c r="A66" s="3"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>159</v>
-      </c>
+      <c r="B66" s="17"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
     </row>
     <row r="67" spans="1:6" ht="30">
       <c r="A67" s="3"/>
       <c r="B67" s="15"/>
       <c r="C67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30">
+      <c r="A68" s="3"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F68" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="3"/>
-      <c r="B68" s="4"/>
-    </row>
-    <row r="69" spans="1:6" ht="18">
-      <c r="A69" s="21" t="s">
+    <row r="69" spans="1:6">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" ht="18">
+      <c r="A70" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="22"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-    </row>
-    <row r="70" spans="1:6" ht="105">
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="22"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+    </row>
+    <row r="71" spans="1:6" ht="105">
+      <c r="B71" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F71" s="11" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="150">
-      <c r="B71" s="20" t="s">
+    <row r="72" spans="1:6" ht="150">
+      <c r="B72" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F72" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="135">
-      <c r="B72" s="20" t="s">
+    <row r="73" spans="1:6" ht="135">
+      <c r="B73" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C73" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F73" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="105">
-      <c r="B73" s="20" t="s">
+    <row r="74" spans="1:6" ht="105">
+      <c r="B74" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F74" s="11" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="120">
-      <c r="B74" s="20" t="s">
+    <row r="75" spans="1:6" ht="120">
+      <c r="B75" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C75" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F75" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="2"/>
-    </row>
-    <row r="76" spans="1:6" ht="120">
-      <c r="F76" s="10" t="s">
+    <row r="76" spans="1:6">
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" ht="120">
+      <c r="F77" s="10" t="s">
         <v>201</v>
       </c>
     </row>

--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -1,33 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D390C9-1FED-4E47-B525-D8E08FE5F78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42954548-1F10-4E83-88E1-1CBA734FA1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="398">
   <si>
     <t>Клиенты и точки входа</t>
   </si>
@@ -1187,12 +1202,438 @@
   <si>
     <t>БД реестра схем</t>
   </si>
+  <si>
+    <t>PPE Adapter</t>
+  </si>
+  <si>
+    <t>Обеспечивает двустороннюю интеграцию с Pricing/Promo Engine (PPE)  для получения триггеров о предстоящих акциях и предварительной предзагрузки кэша перед ожидаемым ростом нагрузки</t>
+  </si>
+  <si>
+    <t>Получение прогнозов событий</t>
+  </si>
+  <si>
+    <t>Адаптер прогнозов (PPE)</t>
+  </si>
+  <si>
+    <t>Кэш лояльности</t>
+  </si>
+  <si>
+    <t>Сервис агрегации метрик</t>
+  </si>
+  <si>
+    <t>Захват изменений (CDC)</t>
+  </si>
+  <si>
+    <t>Адаптеры (POS/WMS/OMS/PPE)</t>
+  </si>
+  <si>
+    <t>Адаптер службы доставки</t>
+  </si>
+  <si>
+    <t>Распределенный кеш</t>
+  </si>
+  <si>
+    <t>БД прогрева кэша</t>
+  </si>
+  <si>
+    <t>PostgreSQL хранилища событий (конфигурация отказоустойчивости)</t>
+  </si>
+  <si>
+    <t>Event Bus (Kafka)</t>
+  </si>
+  <si>
+    <t>Хранилище модели чтения (MongoDB)</t>
+  </si>
+  <si>
+    <t>Load Ballancer</t>
+  </si>
+  <si>
+    <t>Система логирования</t>
+  </si>
+  <si>
+    <t>Система мониторинга и трассировки</t>
+  </si>
+  <si>
+    <t>Оповещение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МП My eDA </t>
+  </si>
+  <si>
+    <t>МП ТСД eDA</t>
+  </si>
+  <si>
+    <t>Входной слой</t>
+  </si>
+  <si>
+    <t>Прикладной слой:</t>
+  </si>
+  <si>
+    <t>-- контур чтения</t>
+  </si>
+  <si>
+    <t>-- контур записи и резервирования</t>
+  </si>
+  <si>
+    <t>-- контур событий</t>
+  </si>
+  <si>
+    <t>-- контур интеграций</t>
+  </si>
+  <si>
+    <t>Инфраструктура/наблюдаемость (слой)</t>
+  </si>
+  <si>
+    <t>Слой данных</t>
+  </si>
+  <si>
+    <t>1. Входной слой</t>
+  </si>
+  <si>
+    <t>Источник</t>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Поток / содержание</t>
+  </si>
+  <si>
+    <t>Загрузка статического контента: изображения, JS/CSS, публичные ресурсы</t>
+  </si>
+  <si>
+    <t>Загрузка статического контента</t>
+  </si>
+  <si>
+    <t>Load Balancer</t>
+  </si>
+  <si>
+    <t>HTTPS-запросы проверки наличия, поиска товара, резервирования</t>
+  </si>
+  <si>
+    <t>HTTPS-запросы сотрудников магазина: проверка остатков, сверка, резерв</t>
+  </si>
+  <si>
+    <t>HTTPS-запросы пользователей</t>
+  </si>
+  <si>
+    <t>МП My eDA / Веб-сайт My eDA</t>
+  </si>
+  <si>
+    <t>Возврат статического контента</t>
+  </si>
+  <si>
+    <t>Балансировка входящих HTTPS-запросов</t>
+  </si>
+  <si>
+    <t>Запросы чтения: наличие товара, список магазинов, доступность SKU</t>
+  </si>
+  <si>
+    <t>Команды изменения состояния: создать/изменить операцию</t>
+  </si>
+  <si>
+    <t>Команды создания, подтверждения, отмены резерва</t>
+  </si>
+  <si>
+    <t>Административные запросы</t>
+  </si>
+  <si>
+    <t>Получение/проверка секретов, ключей, сертификатов при старте/ротации</t>
+  </si>
+  <si>
+    <t>1. Контур чтения</t>
+  </si>
+  <si>
+    <t>GET/MGET availability-ключей: наличие товара, доступное количество, reserved_qty</t>
+  </si>
+  <si>
+    <t>Кэшированный ответ по доступности товара</t>
+  </si>
+  <si>
+    <t>Запрос ближайших магазинов по координатам пользователя и радиусу</t>
+  </si>
+  <si>
+    <t>Поиск магазинов в радиусе, фильтрация по координатам</t>
+  </si>
+  <si>
+    <t>Список магазинов-кандидатов</t>
+  </si>
+  <si>
+    <t>Список ближайших магазинов для дальнейшей проверки наличия</t>
+  </si>
+  <si>
+    <t>Чтение read-модели при промахе кэша или необходимости fallback</t>
+  </si>
+  <si>
+    <t>Срез доступности / read-model snapshot</t>
+  </si>
+  <si>
+    <t>Чтение карточки товара, магазина, категории, единиц измерения, ограничений</t>
+  </si>
+  <si>
+    <t>Справочные данные для формирования ответа</t>
+  </si>
+  <si>
+    <t>Запрос признаков клиента / условий лояльности, если они влияют на выдачу</t>
+  </si>
+  <si>
+    <t>Чтение кэшированных данных лояльности</t>
+  </si>
+  <si>
+    <t>Данные лояльности из кэша</t>
+  </si>
+  <si>
+    <t>API Gateway / Сервис запросов</t>
+  </si>
+  <si>
+    <t>Возврат признаков лояльности для ответа</t>
+  </si>
+  <si>
+    <t>Ответ API: наличие, количество, магазины, stale=true при деградации</t>
+  </si>
+  <si>
+    <t>1. Контур записи и резервирования</t>
+  </si>
+  <si>
+    <t>Команды изменения состояния: корректировка, подтверждение, служебные операции</t>
+  </si>
+  <si>
+    <t>Публикация доменных событий командного контура</t>
+  </si>
+  <si>
+    <t>Создание/подтверждение/отмена резерва</t>
+  </si>
+  <si>
+    <t>Захват/освобождение distributed lock по SKU+магазин</t>
+  </si>
+  <si>
+    <t>Результат захвата блокировки: lock acquired / lock rejected</t>
+  </si>
+  <si>
+    <t>INSERT/UPDATE/SELECT резервов, проверка лимитов, изменение статусов</t>
+  </si>
+  <si>
+    <t>Результат транзакции резервирования</t>
+  </si>
+  <si>
+    <t>INCR/DECR reserved_qty, обновление счетчиков активных резервов</t>
+  </si>
+  <si>
+    <t>События ReservationCreated / ReservationConfirmed / ReservationCancelled / ReservationExpired</t>
+  </si>
+  <si>
+    <t>Управление справочниками, настройками, параметрами SLA/TTL</t>
+  </si>
+  <si>
+    <t>Публикация административных событий изменения конфигурации</t>
+  </si>
+  <si>
+    <t>1. Контур событий</t>
+  </si>
+  <si>
+    <t>Поток inventory/reservation events для построения read-модели</t>
+  </si>
+  <si>
+    <t>Обновление read-модели доступности</t>
+  </si>
+  <si>
+    <t>Материализация актуальных availability-ключей</t>
+  </si>
+  <si>
+    <t>События изменения остатков/резервов для инвалидации и обновления кэша</t>
+  </si>
+  <si>
+    <t>DEL/HSET/SET ключей доступности, инвалидация устаревших значений</t>
+  </si>
+  <si>
+    <t>События и сигналы для предварительного прогрева hot SKU / гео-зон</t>
+  </si>
+  <si>
+    <t>Чтение/запись заданий прогрева, статусов, расписаний</t>
+  </si>
+  <si>
+    <t>Предварительная загрузка availability-ключей</t>
+  </si>
+  <si>
+    <t>Поток событий для расчета бизнес- и технических метрик</t>
+  </si>
+  <si>
+    <t>Запись агрегированных метрик и временных рядов</t>
+  </si>
+  <si>
+    <t>События POS/WMS/резервов для выявления конфликтов остатков</t>
+  </si>
+  <si>
+    <t>Запись конфликтов, статусов сверки, аудита решений</t>
+  </si>
+  <si>
+    <t>Корректирующие события после разрешения конфликта</t>
+  </si>
+  <si>
+    <t>Ошибочные/необработанные сообщения в DLQ-топики</t>
+  </si>
+  <si>
+    <t>Загрузчик моделей чтения / Сервис сверки / Сервис синхронизации кеша</t>
+  </si>
+  <si>
+    <t>Повторная обработка после исправления причины ошибки</t>
+  </si>
+  <si>
+    <t>Чтение/запись версий схем событий</t>
+  </si>
+  <si>
+    <t>Загрузчик моделей чтения / Адаптеры / Сервис команд</t>
+  </si>
+  <si>
+    <t>Проверка совместимости Avro-схем перед публикацией/чтением событий</t>
+  </si>
+  <si>
+    <t>Публикация изменений из операционных БД в виде событий</t>
+  </si>
+  <si>
+    <t>1. Контур интеграций</t>
+  </si>
+  <si>
+    <t>События продаж, возвратов, отмен чеков</t>
+  </si>
+  <si>
+    <t>Остатки, поставки, перемещения, приемка</t>
+  </si>
+  <si>
+    <t>Заказы, статусы заказов, отмены</t>
+  </si>
+  <si>
+    <t>Промо-правила, ограничения доступности</t>
+  </si>
+  <si>
+    <t>Проверка схем событий</t>
+  </si>
+  <si>
+    <t>Нормализованные события inventory.events / order.events / promo.events</t>
+  </si>
+  <si>
+    <t>Запрос/получение мастер-данных и финансово-операционных атрибутов</t>
+  </si>
+  <si>
+    <t>Справочные данные, статусы, ограничения</t>
+  </si>
+  <si>
+    <t>Обновление справочников и атрибутов</t>
+  </si>
+  <si>
+    <t>События изменения справочников/мастер-данных</t>
+  </si>
+  <si>
+    <t>Внешние службы доставки</t>
+  </si>
+  <si>
+    <t>Запрос доступности для доставки / статусов исполнения</t>
+  </si>
+  <si>
+    <t>Статусы доставки, подтверждения, ошибки</t>
+  </si>
+  <si>
+    <t>События delivery status / fulfillment status</t>
+  </si>
+  <si>
+    <t>1. Слой данных и архивирование</t>
+  </si>
+  <si>
+    <t>PostgreSQL хранилища событий</t>
+  </si>
+  <si>
+    <t>Архивирование исторических событий и журналов</t>
+  </si>
+  <si>
+    <t>Выгрузка событий в долговременное S3-compatible хранилище</t>
+  </si>
+  <si>
+    <t>Архивация старых метрик и агрегатов</t>
+  </si>
+  <si>
+    <t>Архивация истории резервов</t>
+  </si>
+  <si>
+    <t>Архивация версий справочников при необходимости</t>
+  </si>
+  <si>
+    <t>1. Безопасность</t>
+  </si>
+  <si>
+    <t>Получение сертификатов, ключей, параметров доступа</t>
+  </si>
+  <si>
+    <t>Получение секретов для подключения к Redis/MongoDB/внешним сервисам</t>
+  </si>
+  <si>
+    <t>Получение секретов для БД резервирования и менеджера блокировок</t>
+  </si>
+  <si>
+    <t>Секреты внешних интеграций</t>
+  </si>
+  <si>
+    <t>Сервисы прикладного слоя</t>
+  </si>
+  <si>
+    <t>Ротация секретов, сертификатов, учетных данных</t>
+  </si>
+  <si>
+    <t>Все сервисы</t>
+  </si>
+  <si>
+    <t>События аудита и безопасности</t>
+  </si>
+  <si>
+    <t>1. Наблюдаемость</t>
+  </si>
+  <si>
+    <t>Метрики RPS, latency, 4xx/5xx, rate limit</t>
+  </si>
+  <si>
+    <t>p95/p99 latency, cache hit ratio, ошибки read-path</t>
+  </si>
+  <si>
+    <t>TPS, lock conflicts, ошибки резервирования</t>
+  </si>
+  <si>
+    <t>Redis ops/s, latency, memory, evictions, hit ratio</t>
+  </si>
+  <si>
+    <t>throughput, consumer lag, broker health, ISR</t>
+  </si>
+  <si>
+    <t>WAL lag, fsync latency, checkpoint activity</t>
+  </si>
+  <si>
+    <t>TPS, lock wait, connection pool, replication lag</t>
+  </si>
+  <si>
+    <t>read/write latency, replication lag</t>
+  </si>
+  <si>
+    <t>Application logs, error logs, audit logs</t>
+  </si>
+  <si>
+    <t>Distributed traces, correlation_id, trace_id</t>
+  </si>
+  <si>
+    <t>Алерты по SLO/SLA, lag, latency, error rate</t>
+  </si>
+  <si>
+    <t>Алерты по критическим ошибкам и событиям ИБ</t>
+  </si>
+  <si>
+    <t>SRE / эксплуатация</t>
+  </si>
+  <si>
+    <t>Уведомления об инцидентах</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1239,6 +1680,21 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="11.65"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1284,7 +1740,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1292,11 +1748,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1370,6 +1878,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1388,9 +1928,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1428,7 +1968,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1534,7 +2074,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1676,7 +2216,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1684,7 +2224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC358B7-DB9E-4D8A-87B3-F1C518B618F4}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -1973,755 +2513,770 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="45">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" ht="409.5">
+        <v>256</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" ht="409.5">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="18">
-      <c r="A24" s="16" t="s">
+    <row r="25" spans="1:6" ht="18">
+      <c r="A25" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" ht="60">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="105">
+      <c r="B25" s="17"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+    </row>
+    <row r="26" spans="1:6" ht="60">
       <c r="A26" s="3"/>
       <c r="B26" s="4" t="s">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="45">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="105">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>195</v>
+        <v>51</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="30">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="45">
       <c r="A28" s="3"/>
       <c r="B28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F29" s="11" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18">
-      <c r="A29" s="16" t="s">
+    <row r="30" spans="1:6" ht="18">
+      <c r="A30" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="30" spans="1:6" ht="75">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="45">
+      <c r="B30" s="17"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" ht="75">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>132</v>
+        <v>20</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="75">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="45">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="75">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="105">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30">
       <c r="A34" s="3"/>
       <c r="B34" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="285">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="105">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>104</v>
+        <v>55</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="75">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="285">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="75">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>240</v>
+        <v>23</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>241</v>
+        <v>64</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="165">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="75">
       <c r="A38" s="3"/>
       <c r="B38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>56</v>
+        <v>103</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="30">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="165">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>57</v>
+        <v>108</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>56</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="120">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="120">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F41" s="11" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="3"/>
-      <c r="B41" s="15" t="s">
+    <row r="42" spans="1:7">
+      <c r="A42" s="3"/>
+      <c r="B42" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18">
-      <c r="A42" s="16" t="s">
+    <row r="43" spans="1:7" ht="18">
+      <c r="A43" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-    </row>
-    <row r="43" spans="1:7" ht="150">
-      <c r="A43" s="3"/>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" ht="150">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F44" s="11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="25.5">
-      <c r="B44" s="4" t="s">
+    <row r="45" spans="1:7" ht="25.5">
+      <c r="B45" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="60">
-      <c r="A45" s="3"/>
-      <c r="B45" s="13" t="s">
+    <row r="46" spans="1:7" ht="60">
+      <c r="A46" s="3"/>
+      <c r="B46" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C46" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14" t="s">
+      <c r="D46" s="14"/>
+      <c r="E46" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F46" s="14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18">
-      <c r="A46" s="16" t="s">
+    <row r="47" spans="1:7" ht="18">
+      <c r="A47" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-    </row>
-    <row r="47" spans="1:7" ht="75">
-      <c r="A47" s="3"/>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="17"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" ht="75">
+      <c r="A48" s="3"/>
+      <c r="B48" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C48" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F48" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" ht="30">
-      <c r="A48" s="3"/>
-      <c r="B48" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>143</v>
-      </c>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" ht="30">
       <c r="A49" s="3"/>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30">
+      <c r="A50" s="3"/>
+      <c r="B50" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C50" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F50" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18">
-      <c r="A50" s="16" t="s">
+    <row r="51" spans="1:7" ht="18">
+      <c r="A51" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-    </row>
-    <row r="51" spans="1:7" ht="30">
-      <c r="A51" s="3"/>
-      <c r="B51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="375">
+      <c r="B51" s="17"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+    </row>
+    <row r="52" spans="1:7" ht="30">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="375">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F53" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G52" s="10"/>
-    </row>
-    <row r="53" spans="1:7" ht="18">
-      <c r="A53" s="16" t="s">
+      <c r="G53" s="10"/>
+    </row>
+    <row r="54" spans="1:7" ht="18">
+      <c r="A54" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-    </row>
-    <row r="54" spans="1:7" ht="30">
-      <c r="A54" s="3"/>
-      <c r="B54" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>163</v>
-      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
     </row>
     <row r="55" spans="1:7" ht="30">
       <c r="A55" s="3"/>
       <c r="B55" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="30">
       <c r="A56" s="3"/>
       <c r="B56" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="30">
       <c r="A57" s="3"/>
       <c r="B57" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="75">
+      <c r="A58" s="3"/>
+      <c r="B58" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F58" s="11" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18">
-      <c r="A58" s="16" t="s">
+    <row r="59" spans="1:7" ht="18">
+      <c r="A59" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-    </row>
-    <row r="59" spans="1:7" ht="45">
-      <c r="A59" s="3"/>
-      <c r="B59" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="60">
+      <c r="B59" s="17"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+    </row>
+    <row r="60" spans="1:7" ht="45">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="30">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="60">
       <c r="A61" s="3"/>
       <c r="B61" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="30">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="300">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="30">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="60">
+        <v>146</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="300">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="60">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="45">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E66" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F66" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="18">
-      <c r="A66" s="16" t="s">
+    <row r="67" spans="1:6" ht="18">
+      <c r="A67" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-    </row>
-    <row r="67" spans="1:6" ht="30">
-      <c r="A67" s="3"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>159</v>
-      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
     </row>
     <row r="68" spans="1:6" ht="30">
       <c r="A68" s="3"/>
       <c r="B68" s="15"/>
       <c r="C68" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="30">
+      <c r="A69" s="3"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F69" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-    </row>
-    <row r="70" spans="1:6" ht="18">
-      <c r="A70" s="21" t="s">
+    <row r="70" spans="1:6">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" ht="18">
+      <c r="A71" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-    </row>
-    <row r="71" spans="1:6" ht="105">
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="22"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+    </row>
+    <row r="72" spans="1:6" ht="105">
+      <c r="B72" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F72" s="11" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="150">
-      <c r="B72" s="20" t="s">
+    <row r="73" spans="1:6" ht="150">
+      <c r="B73" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C73" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F73" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="135">
-      <c r="B73" s="20" t="s">
+    <row r="74" spans="1:6" ht="135">
+      <c r="B74" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F74" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="105">
-      <c r="B74" s="20" t="s">
+    <row r="75" spans="1:6" ht="105">
+      <c r="B75" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C75" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F75" s="11" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="120">
-      <c r="B75" s="20" t="s">
+    <row r="76" spans="1:6" ht="120">
+      <c r="B76" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C76" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F76" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="2"/>
-    </row>
-    <row r="77" spans="1:6" ht="120">
-      <c r="F77" s="10" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:6" ht="120">
+      <c r="F78" s="10" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2827,9 +3382,1484 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A4EE27-F9F7-4D2C-A724-37675A5BE28D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="39.140625" style="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="29" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="29" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="29" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="29" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="29" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="29" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="28.5">
+      <c r="A27" s="29" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="29" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="29" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="28" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="30" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="30" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="28" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="28" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44007732-3124-48CF-9F3F-A6232B565BEA}">
+  <dimension ref="A1:C124"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.42578125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="96.5703125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="35"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+    </row>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A3" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A4" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A5" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A6" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A7" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A8" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A9" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A10" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A11" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A12" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A13" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A14" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="36"/>
+      <c r="B16" s="35"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" s="35"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+    </row>
+    <row r="19" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A19" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A20" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A21" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A22" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A23" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A24" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A25" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A26" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A27" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A28" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A29" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A30" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A31" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A32" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A33" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A34" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="36"/>
+      <c r="B35" s="35"/>
+    </row>
+    <row r="36" spans="1:3" ht="30">
+      <c r="A36" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="B36" s="35"/>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A37" s="35"/>
+      <c r="B37" s="35"/>
+    </row>
+    <row r="38" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A40" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A42" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A43" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A44" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A45" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A46" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A47" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A48" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A49" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="36"/>
+      <c r="B50" s="35"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B51" s="35"/>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A52" s="35"/>
+      <c r="B52" s="35"/>
+    </row>
+    <row r="53" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A53" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A54" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A55" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A56" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A57" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A58" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A59" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B59" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A60" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A61" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B61" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A62" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A63" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A64" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B64" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A65" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="33" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A66" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A67" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="57.75" thickBot="1">
+      <c r="A68" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A69" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C69" s="33" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="43.5" thickBot="1">
+      <c r="A70" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" s="33" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A71" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="36"/>
+      <c r="B72" s="35"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="B73" s="35"/>
+    </row>
+    <row r="74" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A74" s="35"/>
+      <c r="B74" s="35"/>
+    </row>
+    <row r="75" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A75" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C75" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A76" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A77" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A78" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A79" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A80" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A81" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A82" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A83" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A84" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A85" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A86" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A87" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A88" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C88" s="33" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="36"/>
+      <c r="B89" s="35"/>
+    </row>
+    <row r="90" spans="1:3" ht="30">
+      <c r="A90" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="B90" s="35"/>
+    </row>
+    <row r="91" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A91" s="35"/>
+      <c r="B91" s="35"/>
+    </row>
+    <row r="92" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A92" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C92" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A93" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A94" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A95" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A96" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A97" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C97" s="33" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="36"/>
+      <c r="B98" s="35"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="34" t="s">
+        <v>374</v>
+      </c>
+      <c r="B99" s="35"/>
+    </row>
+    <row r="100" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A100" s="35"/>
+      <c r="B100" s="35"/>
+    </row>
+    <row r="101" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A101" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C101" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A102" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A103" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="33" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A104" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="33" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A105" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B105" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A106" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="C106" s="33" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A107" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="C107" s="33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="36"/>
+      <c r="B108" s="35"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="B109" s="35"/>
+    </row>
+    <row r="110" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A110" s="35"/>
+      <c r="B110" s="35"/>
+    </row>
+    <row r="111" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A111" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B111" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C111" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A112" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B112" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C112" s="33" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A113" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A114" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A115" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" s="33" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A116" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" s="33" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A117" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C117" s="33" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A118" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C118" s="33" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A119" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B119" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C119" s="33" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A120" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="C120" s="33" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A121" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B121" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C121" s="33" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A122" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A123" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="B123" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="C123" s="33" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A124" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B124" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="C124" s="33" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42954548-1F10-4E83-88E1-1CBA734FA1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FAD485-B82E-4A50-B1F9-F1B81245DE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1804,7 +1804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1872,15 +1872,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1909,6 +1900,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3297,76 +3294,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="26"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
-      <c r="A2" s="25"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60">
-      <c r="A3" s="25"/>
+      <c r="A3" s="36"/>
       <c r="C3" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45">
-      <c r="A4" s="25"/>
+      <c r="A4" s="36"/>
       <c r="C4" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="25"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60">
-      <c r="A6" s="25"/>
+      <c r="A6" s="36"/>
       <c r="C6" s="11" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30">
-      <c r="A7" s="25"/>
+      <c r="A7" s="36"/>
       <c r="C7" s="11" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="25"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60">
-      <c r="A9" s="25"/>
+      <c r="A9" s="36"/>
       <c r="C9" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45">
-      <c r="A10" s="25"/>
+      <c r="A10" s="36"/>
       <c r="C10" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="25"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="75">
-      <c r="A12" s="25"/>
+      <c r="A12" s="36"/>
       <c r="C12" s="7" t="s">
         <v>212</v>
       </c>
@@ -3385,241 +3382,241 @@
   <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="39.140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.140625" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="26" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="26" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="26" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="26" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="26" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="26" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="26" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="26" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="26" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="26" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="26" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="26" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="26" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="26" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="26" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="26" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="26" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="28.5">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="26" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="26" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="26" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="26" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="26" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="26" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="26" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="26" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="25" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="25" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="25" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="25" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="25" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="27" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="27" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="27" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="27" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="25" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="25" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3634,1228 +3631,1228 @@
   <dimension ref="A1:C124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="96.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="28"/>
+    <col min="1" max="1" width="27.42578125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="96.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="30" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="30" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="30" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="30" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="30" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="30" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="34" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="30" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="30" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="30" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="30" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="30" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="30" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="B17" s="35"/>
+      <c r="B17" s="32"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="30" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="30" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="30" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="30" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="30" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="30" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="30" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="30" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="30" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="30" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="30" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="30" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="30" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="30" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="30" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="35"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="1:3" ht="30">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="32"/>
     </row>
     <row r="37" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="30" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="30" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="30" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="30" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="33" t="s">
+      <c r="C43" s="30" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="30" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="30" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="30" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C47" s="33" t="s">
+      <c r="C47" s="30" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="30" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C49" s="33" t="s">
+      <c r="C49" s="30" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="35"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="32"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="B51" s="35"/>
+      <c r="B51" s="32"/>
     </row>
     <row r="52" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A52" s="35"/>
-      <c r="B52" s="35"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
     </row>
     <row r="53" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C53" s="32" t="s">
+      <c r="C53" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B54" s="33" t="s">
+      <c r="B54" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="C54" s="33" t="s">
+      <c r="C54" s="30" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="B55" s="33" t="s">
+      <c r="B55" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="30" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="C56" s="33" t="s">
+      <c r="C56" s="30" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C57" s="30" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="B58" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="30" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="33" t="s">
+      <c r="C59" s="30" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="B60" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="C60" s="33" t="s">
+      <c r="C60" s="30" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="33" t="s">
+      <c r="B61" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="C61" s="33" t="s">
+      <c r="C61" s="30" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="C62" s="33" t="s">
+      <c r="C62" s="30" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="B63" s="33" t="s">
+      <c r="B63" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C63" s="33" t="s">
+      <c r="C63" s="30" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="33" t="s">
+      <c r="C64" s="30" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="B65" s="33" t="s">
+      <c r="B65" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="33" t="s">
+      <c r="C65" s="30" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="33" t="s">
+      <c r="B66" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C66" s="33" t="s">
+      <c r="C66" s="30" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B67" s="33" t="s">
+      <c r="B67" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="C67" s="33" t="s">
+      <c r="C67" s="30" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="57.75" thickBot="1">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="B68" s="33" t="s">
+      <c r="B68" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="C68" s="33" t="s">
+      <c r="C68" s="30" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B69" s="33" t="s">
+      <c r="B69" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="C69" s="33" t="s">
+      <c r="C69" s="30" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="43.5" thickBot="1">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="B70" s="33" t="s">
+      <c r="B70" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C70" s="33" t="s">
+      <c r="C70" s="30" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C71" s="33" t="s">
+      <c r="C71" s="30" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="36"/>
-      <c r="B72" s="35"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="32"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="34" t="s">
+      <c r="A73" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="B73" s="35"/>
+      <c r="B73" s="32"/>
     </row>
     <row r="74" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="32"/>
     </row>
     <row r="75" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A75" s="31" t="s">
+      <c r="A75" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C75" s="32" t="s">
+      <c r="C75" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C76" s="33" t="s">
+      <c r="C76" s="30" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A77" s="27" t="s">
+      <c r="A77" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="33" t="s">
+      <c r="B77" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C77" s="33" t="s">
+      <c r="C77" s="30" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A78" s="27" t="s">
+      <c r="A78" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="C78" s="30" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A79" s="27" t="s">
+      <c r="A79" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C79" s="33" t="s">
+      <c r="C79" s="30" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A80" s="27" t="s">
+      <c r="A80" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C80" s="33" t="s">
+      <c r="C80" s="30" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="B81" s="33" t="s">
+      <c r="B81" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C81" s="33" t="s">
+      <c r="C81" s="30" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C82" s="33" t="s">
+      <c r="C82" s="30" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A83" s="27" t="s">
+      <c r="A83" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="C83" s="33" t="s">
+      <c r="C83" s="30" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C84" s="33" t="s">
+      <c r="C84" s="30" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A85" s="27" t="s">
+      <c r="A85" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C85" s="33" t="s">
+      <c r="C85" s="30" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A86" s="27" t="s">
+      <c r="A86" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="35" t="s">
         <v>363</v>
       </c>
-      <c r="C86" s="33" t="s">
+      <c r="C86" s="30" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A87" s="27" t="s">
+      <c r="A87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="C87" s="33" t="s">
+      <c r="C87" s="30" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A88" s="27" t="s">
+      <c r="A88" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="B88" s="33" t="s">
+      <c r="B88" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="C88" s="33" t="s">
+      <c r="C88" s="30" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="36"/>
-      <c r="B89" s="35"/>
+      <c r="A89" s="33"/>
+      <c r="B89" s="32"/>
     </row>
     <row r="90" spans="1:3" ht="30">
-      <c r="A90" s="34" t="s">
+      <c r="A90" s="31" t="s">
         <v>367</v>
       </c>
-      <c r="B90" s="35"/>
+      <c r="B90" s="32"/>
     </row>
     <row r="91" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A91" s="35"/>
-      <c r="B91" s="35"/>
+      <c r="A91" s="32"/>
+      <c r="B91" s="32"/>
     </row>
     <row r="92" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A92" s="31" t="s">
+      <c r="A92" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B92" s="32" t="s">
+      <c r="B92" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C92" s="32" t="s">
+      <c r="C92" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A93" s="27" t="s">
+      <c r="A93" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="B93" s="33" t="s">
+      <c r="B93" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="C93" s="33" t="s">
+      <c r="C93" s="30" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B94" s="33" t="s">
+      <c r="B94" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="C94" s="33" t="s">
+      <c r="C94" s="30" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A95" s="27" t="s">
+      <c r="A95" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="B95" s="33" t="s">
+      <c r="B95" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="C95" s="33" t="s">
+      <c r="C95" s="30" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B96" s="33" t="s">
+      <c r="B96" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="C96" s="33" t="s">
+      <c r="C96" s="30" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A97" s="27" t="s">
+      <c r="A97" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="B97" s="33" t="s">
+      <c r="B97" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="C97" s="33" t="s">
+      <c r="C97" s="30" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="36"/>
-      <c r="B98" s="35"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="32"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="34" t="s">
+      <c r="A99" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B99" s="35"/>
+      <c r="B99" s="32"/>
     </row>
     <row r="100" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A100" s="35"/>
-      <c r="B100" s="35"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="32"/>
     </row>
     <row r="101" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A101" s="31" t="s">
+      <c r="A101" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B101" s="32" t="s">
+      <c r="B101" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C101" s="32" t="s">
+      <c r="C101" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A102" s="27" t="s">
+      <c r="A102" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B102" s="33" t="s">
+      <c r="B102" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="33" t="s">
+      <c r="C102" s="30" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A103" s="27" t="s">
+      <c r="A103" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B103" s="33" t="s">
+      <c r="B103" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="33" t="s">
+      <c r="C103" s="30" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A104" s="27" t="s">
+      <c r="A104" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="33" t="s">
+      <c r="C104" s="30" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A105" s="27" t="s">
+      <c r="A105" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="B105" s="33" t="s">
+      <c r="B105" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="33" t="s">
+      <c r="C105" s="30" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A106" s="27" t="s">
+      <c r="A106" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B106" s="33" t="s">
+      <c r="B106" s="35" t="s">
         <v>379</v>
       </c>
-      <c r="C106" s="33" t="s">
+      <c r="C106" s="30" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A107" s="27" t="s">
+      <c r="A107" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="B107" s="33" t="s">
+      <c r="B107" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="C107" s="33" t="s">
+      <c r="C107" s="30" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="36"/>
-      <c r="B108" s="35"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="32"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="34" t="s">
+      <c r="A109" s="31" t="s">
         <v>383</v>
       </c>
-      <c r="B109" s="35"/>
+      <c r="B109" s="32"/>
     </row>
     <row r="110" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A110" s="35"/>
-      <c r="B110" s="35"/>
+      <c r="A110" s="32"/>
+      <c r="B110" s="32"/>
     </row>
     <row r="111" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A111" s="31" t="s">
+      <c r="A111" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B111" s="32" t="s">
+      <c r="B111" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="C111" s="32" t="s">
+      <c r="C111" s="29" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A112" s="27" t="s">
+      <c r="A112" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B112" s="33" t="s">
+      <c r="B112" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C112" s="33" t="s">
+      <c r="C112" s="30" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A113" s="27" t="s">
+      <c r="A113" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C113" s="33" t="s">
+      <c r="C113" s="30" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A114" s="27" t="s">
+      <c r="A114" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B114" s="33" t="s">
+      <c r="B114" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C114" s="30" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="B115" s="33" t="s">
+      <c r="B115" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C115" s="33" t="s">
+      <c r="C115" s="30" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A116" s="27" t="s">
+      <c r="A116" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B116" s="33" t="s">
+      <c r="B116" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C116" s="33" t="s">
+      <c r="C116" s="30" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A117" s="27" t="s">
+      <c r="A117" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="B117" s="33" t="s">
+      <c r="B117" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C117" s="33" t="s">
+      <c r="C117" s="30" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A118" s="27" t="s">
+      <c r="A118" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B118" s="33" t="s">
+      <c r="B118" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C118" s="33" t="s">
+      <c r="C118" s="30" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A119" s="27" t="s">
+      <c r="A119" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B119" s="33" t="s">
+      <c r="B119" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C119" s="33" t="s">
+      <c r="C119" s="30" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="B120" s="33" t="s">
+      <c r="B120" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="C120" s="33" t="s">
+      <c r="C120" s="30" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A121" s="27" t="s">
+      <c r="A121" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="B121" s="33" t="s">
+      <c r="B121" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="33" t="s">
+      <c r="C121" s="30" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A122" s="27" t="s">
+      <c r="A122" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="33" t="s">
+      <c r="B122" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="C122" s="30" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B123" s="33" t="s">
+      <c r="B123" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C123" s="33" t="s">
+      <c r="C123" s="30" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A124" s="27" t="s">
+      <c r="A124" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="B124" s="33" t="s">
+      <c r="B124" s="35" t="s">
         <v>396</v>
       </c>
-      <c r="C124" s="33" t="s">
+      <c r="C124" s="30" t="s">
         <v>397</v>
       </c>
     </row>

--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FAD485-B82E-4A50-B1F9-F1B81245DE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B156A50-6238-4F53-81B7-B3ED66C704FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>In-Memory Key-Value Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event Store </t>
   </si>
   <si>
     <t>Append-only Log или Immutable Event Database</t>
@@ -1627,6 +1624,35 @@
   </si>
   <si>
     <t>Уведомления об инцидентах</t>
+  </si>
+  <si>
+    <r>
+      <t>Event Store 
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PostgreSQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2252,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30">
@@ -2264,7 +2290,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="75">
@@ -2276,7 +2302,7 @@
         <v>9</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60">
@@ -2288,7 +2314,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45">
@@ -2300,7 +2326,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18">
@@ -2369,10 +2395,10 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="270">
@@ -2385,10 +2411,10 @@
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45">
@@ -2471,7 +2497,7 @@
         <v>94</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>42</v>
@@ -2486,7 +2512,7 @@
         <v>95</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>43</v>
@@ -2501,7 +2527,7 @@
         <v>96</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>44</v>
@@ -2513,25 +2539,25 @@
     <row r="22" spans="1:6" ht="45">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -2549,7 +2575,7 @@
         <v>46</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18">
@@ -2565,16 +2591,16 @@
     <row r="26" spans="1:6" ht="60">
       <c r="A26" s="3"/>
       <c r="B26" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>50</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="105">
@@ -2589,7 +2615,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="45">
@@ -2601,10 +2627,10 @@
         <v>48</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30">
@@ -2619,7 +2645,7 @@
         <v>52</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18">
@@ -2647,7 +2673,7 @@
         <v>60</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45">
@@ -2656,13 +2682,13 @@
         <v>21</v>
       </c>
       <c r="C32" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>133</v>
-      </c>
       <c r="E32" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>128</v>
@@ -2677,10 +2703,10 @@
         <v>53</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>126</v>
@@ -2695,7 +2721,7 @@
         <v>54</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>61</v>
@@ -2713,7 +2739,7 @@
         <v>55</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>62</v>
@@ -2734,7 +2760,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="75">
@@ -2749,7 +2775,7 @@
         <v>64</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="75">
@@ -2761,13 +2787,13 @@
         <v>106</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="F38" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="165">
@@ -2779,60 +2805,60 @@
         <v>56</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>65</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="120">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>131</v>
       </c>
       <c r="E41" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3"/>
       <c r="B42" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18">
       <c r="A43" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
@@ -2849,24 +2875,24 @@
         <v>58</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>66</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.5">
       <c r="B45" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="60">
@@ -2882,12 +2908,12 @@
         <v>67</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="18">
       <c r="A47" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="19"/>
@@ -2898,13 +2924,13 @@
     <row r="48" spans="1:7" ht="75">
       <c r="A48" s="3"/>
       <c r="B48" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G48" s="2"/>
     </row>
@@ -2917,7 +2943,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30">
@@ -2926,13 +2952,13 @@
         <v>27</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>70</v>
@@ -2940,7 +2966,7 @@
     </row>
     <row r="51" spans="1:7" ht="18">
       <c r="A51" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="19"/>
@@ -2954,34 +2980,34 @@
         <v>26</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="375">
       <c r="A53" s="3"/>
       <c r="B53" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G53" s="10"/>
     </row>
     <row r="54" spans="1:7" ht="18">
       <c r="A54" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="19"/>
@@ -2995,13 +3021,13 @@
         <v>28</v>
       </c>
       <c r="C55" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="30">
@@ -3010,13 +3036,13 @@
         <v>29</v>
       </c>
       <c r="C56" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E56" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="F56" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="30">
@@ -3025,13 +3051,13 @@
         <v>30</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E57" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="F57" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="75">
@@ -3043,10 +3069,10 @@
         <v>68</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="18">
@@ -3071,7 +3097,7 @@
         <v>71</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="60">
@@ -3086,7 +3112,7 @@
         <v>72</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="30">
@@ -3101,7 +3127,7 @@
         <v>73</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="30">
@@ -3116,10 +3142,10 @@
         <v>74</v>
       </c>
       <c r="F63" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G63" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="300">
@@ -3134,7 +3160,7 @@
         <v>75</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="60">
@@ -3149,7 +3175,7 @@
         <v>76</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="45">
@@ -3164,12 +3190,12 @@
         <v>115</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="18">
       <c r="A67" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="19"/>
@@ -3181,23 +3207,23 @@
       <c r="A68" s="3"/>
       <c r="B68" s="15"/>
       <c r="C68" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="30">
       <c r="A69" s="3"/>
       <c r="B69" s="15"/>
       <c r="C69" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3206,7 +3232,7 @@
     </row>
     <row r="71" spans="1:6" ht="18">
       <c r="A71" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="23"/>
@@ -3216,57 +3242,57 @@
     </row>
     <row r="72" spans="1:6" ht="105">
       <c r="B72" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="150">
       <c r="B73" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="135">
       <c r="B74" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="105">
       <c r="B75" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="120">
       <c r="B76" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3274,7 +3300,7 @@
     </row>
     <row r="78" spans="1:6" ht="120">
       <c r="F78" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3295,77 +3321,77 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="37" t="s">
         <v>213</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>214</v>
       </c>
       <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="36"/>
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60">
       <c r="A3" s="36"/>
       <c r="C3" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45">
       <c r="A4" s="36"/>
       <c r="C4" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="36"/>
       <c r="B5" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60">
       <c r="A6" s="36"/>
       <c r="C6" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30">
       <c r="A7" s="36"/>
       <c r="C7" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="36"/>
       <c r="B8" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60">
       <c r="A9" s="36"/>
       <c r="C9" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45">
       <c r="A10" s="36"/>
       <c r="C10" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="36"/>
       <c r="B11" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="75">
       <c r="A12" s="36"/>
       <c r="C12" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3448,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3442,12 +3468,12 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3462,12 +3488,12 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -3482,22 +3508,22 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -3507,7 +3533,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -3517,17 +3543,17 @@
     </row>
     <row r="27" spans="1:1" ht="28.5">
       <c r="A27" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -3537,7 +3563,7 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -3547,27 +3573,27 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -3582,42 +3608,42 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3639,7 +3665,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B1" s="32"/>
     </row>
@@ -3649,13 +3675,13 @@
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
       <c r="A3" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
@@ -3666,7 +3692,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1">
@@ -3677,7 +3703,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1">
@@ -3685,21 +3711,21 @@
         <v>84</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>290</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1">
       <c r="A7" s="34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1">
@@ -3707,10 +3733,10 @@
         <v>85</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="29.25" thickBot="1">
@@ -3718,21 +3744,21 @@
         <v>13</v>
       </c>
       <c r="B9" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>294</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1">
       <c r="A10" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1">
@@ -3743,7 +3769,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1">
@@ -3754,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1">
@@ -3765,7 +3791,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
@@ -3776,7 +3802,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" thickBot="1">
@@ -3787,7 +3813,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3796,7 +3822,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B17" s="32"/>
     </row>
@@ -3806,13 +3832,13 @@
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
       <c r="A19" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="C19" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1">
@@ -3820,21 +3846,21 @@
         <v>15</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1">
       <c r="A21" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1">
@@ -3845,7 +3871,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
@@ -3856,7 +3882,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1">
@@ -3867,7 +3893,7 @@
         <v>18</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
@@ -3878,7 +3904,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="29.25" thickBot="1">
@@ -3886,21 +3912,21 @@
         <v>15</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="29.25" thickBot="1">
       <c r="A27" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" s="35" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="29.25" thickBot="1">
@@ -3911,7 +3937,7 @@
         <v>102</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1">
@@ -3922,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1">
@@ -3933,7 +3959,7 @@
         <v>100</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1">
@@ -3941,21 +3967,21 @@
         <v>100</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1">
       <c r="A32" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B32" s="35" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="29.25" thickBot="1">
@@ -3963,10 +3989,10 @@
         <v>100</v>
       </c>
       <c r="B33" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="30" t="s">
         <v>316</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1">
@@ -3977,7 +4003,7 @@
         <v>88</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3986,7 +4012,7 @@
     </row>
     <row r="36" spans="1:3" ht="30">
       <c r="A36" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B36" s="32"/>
     </row>
@@ -3996,13 +4022,13 @@
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
       <c r="A38" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="C38" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" thickBot="1">
@@ -4013,7 +4039,7 @@
         <v>16</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" thickBot="1">
@@ -4021,10 +4047,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" thickBot="1">
@@ -4035,7 +4061,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" thickBot="1">
@@ -4046,7 +4072,7 @@
         <v>27</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" thickBot="1">
@@ -4057,7 +4083,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" thickBot="1">
@@ -4068,7 +4094,7 @@
         <v>22</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" thickBot="1">
@@ -4079,7 +4105,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" thickBot="1">
@@ -4087,10 +4113,10 @@
         <v>17</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" thickBot="1">
@@ -4098,10 +4124,10 @@
         <v>17</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="29.25" thickBot="1">
@@ -4112,7 +4138,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" thickBot="1">
@@ -4120,10 +4146,10 @@
         <v>19</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4132,7 +4158,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B51" s="32"/>
     </row>
@@ -4142,57 +4168,57 @@
     </row>
     <row r="53" spans="1:3" ht="17.25" thickBot="1">
       <c r="A53" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B53" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="C53" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="29.25" thickBot="1">
       <c r="A54" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="29.25" thickBot="1">
       <c r="A55" s="34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" thickBot="1">
       <c r="A56" s="34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="29.25" thickBot="1">
       <c r="A57" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B57" s="35" t="s">
         <v>99</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="29.25" thickBot="1">
@@ -4200,21 +4226,21 @@
         <v>99</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" thickBot="1">
       <c r="A59" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B59" s="35" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" thickBot="1">
@@ -4222,10 +4248,10 @@
         <v>98</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" thickBot="1">
@@ -4233,43 +4259,43 @@
         <v>98</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="29.25" thickBot="1">
       <c r="A62" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="29.25" thickBot="1">
       <c r="A63" s="34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B63" s="35" t="s">
         <v>108</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" thickBot="1">
       <c r="A64" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B64" s="35" t="s">
         <v>93</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" thickBot="1">
@@ -4280,7 +4306,7 @@
         <v>23</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" thickBot="1">
@@ -4288,32 +4314,32 @@
         <v>93</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" thickBot="1">
       <c r="A67" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="57.75" thickBot="1">
       <c r="A68" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="C68" s="30" t="s">
         <v>346</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" thickBot="1">
@@ -4321,32 +4347,32 @@
         <v>25</v>
       </c>
       <c r="B69" s="35" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="43.5" thickBot="1">
       <c r="A70" s="34" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B70" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" thickBot="1">
       <c r="A71" s="34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B71" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -4355,7 +4381,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="31" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B73" s="32"/>
     </row>
@@ -4365,13 +4391,13 @@
     </row>
     <row r="75" spans="1:3" ht="17.25" thickBot="1">
       <c r="A75" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B75" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B75" s="29" t="s">
+      <c r="C75" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C75" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="29.25" thickBot="1">
@@ -4379,10 +4405,10 @@
         <v>83</v>
       </c>
       <c r="B76" s="35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="29.25" thickBot="1">
@@ -4390,10 +4416,10 @@
         <v>82</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="29.25" thickBot="1">
@@ -4401,10 +4427,10 @@
         <v>81</v>
       </c>
       <c r="B78" s="35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="29.25" thickBot="1">
@@ -4412,43 +4438,43 @@
         <v>79</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="29.25" thickBot="1">
       <c r="A80" s="34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B80" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="29.25" thickBot="1">
       <c r="A81" s="34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" thickBot="1">
       <c r="A82" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B82" s="35" t="s">
         <v>80</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" thickBot="1">
@@ -4456,65 +4482,65 @@
         <v>80</v>
       </c>
       <c r="B83" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="29.25" thickBot="1">
       <c r="A84" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B84" s="35" t="s">
         <v>102</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" thickBot="1">
       <c r="A85" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="29.25" thickBot="1">
       <c r="A86" s="34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B86" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="C86" s="30" t="s">
         <v>363</v>
-      </c>
-      <c r="C86" s="30" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="29.25" thickBot="1">
       <c r="A87" s="34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" thickBot="1">
       <c r="A88" s="34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4523,7 +4549,7 @@
     </row>
     <row r="90" spans="1:3" ht="30">
       <c r="A90" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B90" s="32"/>
     </row>
@@ -4533,35 +4559,35 @@
     </row>
     <row r="92" spans="1:3" ht="17.25" thickBot="1">
       <c r="A92" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B92" s="29" t="s">
+      <c r="C92" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C92" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="29.25" thickBot="1">
       <c r="A93" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="B93" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="C93" s="30" t="s">
         <v>368</v>
-      </c>
-      <c r="B93" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="C93" s="30" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" thickBot="1">
       <c r="A94" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B94" s="35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="29.25" thickBot="1">
@@ -4569,10 +4595,10 @@
         <v>108</v>
       </c>
       <c r="B95" s="35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" thickBot="1">
@@ -4580,10 +4606,10 @@
         <v>22</v>
       </c>
       <c r="B96" s="35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" thickBot="1">
@@ -4591,10 +4617,10 @@
         <v>102</v>
       </c>
       <c r="B97" s="35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4603,7 +4629,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B99" s="32"/>
     </row>
@@ -4613,13 +4639,13 @@
     </row>
     <row r="101" spans="1:3" ht="17.25" thickBot="1">
       <c r="A101" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B101" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B101" s="29" t="s">
+      <c r="C101" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C101" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" thickBot="1">
@@ -4630,7 +4656,7 @@
         <v>26</v>
       </c>
       <c r="C102" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" thickBot="1">
@@ -4641,7 +4667,7 @@
         <v>26</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" thickBot="1">
@@ -4652,18 +4678,18 @@
         <v>26</v>
       </c>
       <c r="C104" s="30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="29.25" thickBot="1">
       <c r="A105" s="34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B105" s="35" t="s">
         <v>26</v>
       </c>
       <c r="C105" s="30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="29.25" thickBot="1">
@@ -4671,21 +4697,21 @@
         <v>26</v>
       </c>
       <c r="B106" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="C106" s="30" t="s">
         <v>379</v>
-      </c>
-      <c r="C106" s="30" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" thickBot="1">
       <c r="A107" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="B107" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="C107" s="30" t="s">
         <v>381</v>
-      </c>
-      <c r="B107" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="C107" s="30" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -4694,7 +4720,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B109" s="32"/>
     </row>
@@ -4704,13 +4730,13 @@
     </row>
     <row r="111" spans="1:3" ht="17.25" thickBot="1">
       <c r="A111" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B111" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="C111" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="C111" s="29" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="29.25" thickBot="1">
@@ -4718,10 +4744,10 @@
         <v>88</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C112" s="30" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="29.25" thickBot="1">
@@ -4729,10 +4755,10 @@
         <v>15</v>
       </c>
       <c r="B113" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C113" s="30" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="29.25" thickBot="1">
@@ -4740,43 +4766,43 @@
         <v>17</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="29.25" thickBot="1">
       <c r="A115" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B115" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C115" s="30" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="29.25" thickBot="1">
       <c r="A116" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C116" s="30" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="29.25" thickBot="1">
       <c r="A117" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B117" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="29.25" thickBot="1">
@@ -4784,76 +4810,76 @@
         <v>22</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="29.25" thickBot="1">
       <c r="A119" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B119" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" thickBot="1">
       <c r="A120" s="34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="29.25" thickBot="1">
       <c r="A121" s="34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C121" s="30" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="29.25" thickBot="1">
       <c r="A122" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="35" t="s">
-        <v>273</v>
-      </c>
       <c r="C122" s="30" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" thickBot="1">
       <c r="A123" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B123" s="35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C123" s="30" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" thickBot="1">
       <c r="A124" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B124" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="C124" s="30" t="s">
         <v>396</v>
-      </c>
-      <c r="C124" s="30" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B156A50-6238-4F53-81B7-B3ED66C704FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D4874B-77C6-4869-BB37-477BFEFBEBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
-    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
+    <sheet name="Лист2" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/doc/рассчет/Компоненты сервиса eDA.xlsx
+++ b/doc/рассчет/Компоненты сервиса eDA.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D4874B-77C6-4869-BB37-477BFEFBEBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AD3832-69ED-4A39-8854-76EAD2B7AEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{017D0FF2-70E3-4140-A88B-BECF84AB06A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="Лист4" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Лист5" sheetId="5" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Лист3" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Лист4" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2248,14 +2249,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC358B7-DB9E-4D8A-87B3-F1C518B618F4}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="11" customWidth="1"/>
     <col min="4" max="4" width="22" style="11" customWidth="1"/>
     <col min="5" max="5" width="29" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="81.85546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="81.88671875" style="11" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2269,7 +2270,7 @@
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
     </row>
-    <row r="2" spans="1:6" ht="60">
+    <row r="2" spans="1:6" ht="57.6">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>84</v>
@@ -2281,7 +2282,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30">
+    <row r="3" spans="1:6" ht="28.8">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>85</v>
@@ -2293,7 +2294,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="75">
+    <row r="4" spans="1:6" ht="57.6">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
         <v>86</v>
@@ -2305,7 +2306,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="60">
+    <row r="5" spans="1:6" ht="43.2">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
         <v>87</v>
@@ -2317,7 +2318,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45">
+    <row r="6" spans="1:6" ht="43.2">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
         <v>12</v>
@@ -2339,7 +2340,7 @@
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
     </row>
-    <row r="8" spans="1:6" ht="63.75">
+    <row r="8" spans="1:6" ht="66">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
         <v>88</v>
@@ -2351,7 +2352,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30">
+    <row r="9" spans="1:6" ht="28.8">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
         <v>90</v>
@@ -2363,7 +2364,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30">
+    <row r="10" spans="1:6" ht="28.8">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
@@ -2385,7 +2386,7 @@
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
     </row>
-    <row r="12" spans="1:6" ht="135">
+    <row r="12" spans="1:6" ht="115.2">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
         <v>15</v>
@@ -2401,7 +2402,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="270">
+    <row r="13" spans="1:6" ht="244.8">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
         <v>16</v>
@@ -2417,7 +2418,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45">
+    <row r="14" spans="1:6" ht="43.2">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
         <v>17</v>
@@ -2433,7 +2434,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="38.25">
+    <row r="15" spans="1:6" ht="39.6">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
         <v>18</v>
@@ -2449,7 +2450,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45">
+    <row r="16" spans="1:6" ht="43.2">
       <c r="A16" s="3"/>
       <c r="B16" s="6" t="s">
         <v>93</v>
@@ -2465,7 +2466,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="75">
+    <row r="17" spans="1:6" ht="72">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
         <v>19</v>
@@ -2491,7 +2492,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="19"/>
     </row>
-    <row r="19" spans="1:6" ht="45">
+    <row r="19" spans="1:6" ht="43.2">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
         <v>94</v>
@@ -2506,7 +2507,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="45">
+    <row r="20" spans="1:6" ht="28.8">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
         <v>95</v>
@@ -2521,7 +2522,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30">
+    <row r="21" spans="1:6" ht="28.8">
       <c r="A21" s="3"/>
       <c r="B21" s="4" t="s">
         <v>96</v>
@@ -2536,7 +2537,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="45">
+    <row r="22" spans="1:6" ht="43.2">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
         <v>258</v>
@@ -2563,7 +2564,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="1:6" ht="409.5">
+    <row r="24" spans="1:6" ht="360">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
         <v>97</v>
@@ -2588,7 +2589,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
     </row>
-    <row r="26" spans="1:6" ht="60">
+    <row r="26" spans="1:6" ht="57.6">
       <c r="A26" s="3"/>
       <c r="B26" s="4" t="s">
         <v>216</v>
@@ -2603,7 +2604,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="105">
+    <row r="27" spans="1:6" ht="72">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
         <v>98</v>
@@ -2618,7 +2619,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="45">
+    <row r="28" spans="1:6" ht="43.2">
       <c r="A28" s="3"/>
       <c r="B28" s="4" t="s">
         <v>99</v>
@@ -2633,7 +2634,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="30">
+    <row r="29" spans="1:6" ht="28.8">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
         <v>100</v>
@@ -2658,7 +2659,7 @@
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
     </row>
-    <row r="31" spans="1:6" ht="75">
+    <row r="31" spans="1:6" ht="72">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
         <v>20</v>
@@ -2676,7 +2677,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="45">
+    <row r="32" spans="1:6" ht="43.2">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
         <v>21</v>
@@ -2694,7 +2695,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="75">
+    <row r="33" spans="1:7" ht="72">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
         <v>107</v>
@@ -2712,7 +2713,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30">
+    <row r="34" spans="1:7" ht="28.8">
       <c r="A34" s="3"/>
       <c r="B34" s="4" t="s">
         <v>101</v>
@@ -2730,7 +2731,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="105">
+    <row r="35" spans="1:7" ht="100.8">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
         <v>102</v>
@@ -2748,7 +2749,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="285">
+    <row r="36" spans="1:7" ht="273.60000000000002">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
         <v>22</v>
@@ -2763,7 +2764,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="75">
+    <row r="37" spans="1:7" ht="57.6">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
         <v>23</v>
@@ -2778,7 +2779,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="75">
+    <row r="38" spans="1:7" ht="72">
       <c r="A38" s="3"/>
       <c r="B38" s="4" t="s">
         <v>103</v>
@@ -2796,7 +2797,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="165">
+    <row r="39" spans="1:7" ht="144">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
         <v>108</v>
@@ -2814,7 +2815,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30">
+    <row r="40" spans="1:7" ht="28.8">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
         <v>248</v>
@@ -2832,7 +2833,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="120">
+    <row r="41" spans="1:7" ht="115.2">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
         <v>218</v>
@@ -2866,7 +2867,7 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
     </row>
-    <row r="44" spans="1:7" ht="150">
+    <row r="44" spans="1:7" ht="129.6">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
         <v>24</v>
@@ -2884,7 +2885,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="25.5">
+    <row r="45" spans="1:7" ht="26.4">
       <c r="B45" s="4" t="s">
         <v>242</v>
       </c>
@@ -2895,7 +2896,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="60">
+    <row r="46" spans="1:7" ht="43.2">
       <c r="A46" s="3"/>
       <c r="B46" s="13" t="s">
         <v>25</v>
@@ -2921,7 +2922,7 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
     </row>
-    <row r="48" spans="1:7" ht="75">
+    <row r="48" spans="1:7" ht="72">
       <c r="A48" s="3"/>
       <c r="B48" s="15" t="s">
         <v>247</v>
@@ -2934,7 +2935,7 @@
       </c>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" ht="30">
+    <row r="49" spans="1:7" ht="28.8">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
         <v>99</v>
@@ -2946,7 +2947,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30">
+    <row r="50" spans="1:7" ht="28.8">
       <c r="A50" s="3"/>
       <c r="B50" s="8" t="s">
         <v>27</v>
@@ -2974,7 +2975,7 @@
       <c r="E51" s="19"/>
       <c r="F51" s="19"/>
     </row>
-    <row r="52" spans="1:7" ht="30">
+    <row r="52" spans="1:7" ht="28.8">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
         <v>26</v>
@@ -2989,7 +2990,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="375">
+    <row r="53" spans="1:7" ht="345.6">
       <c r="A53" s="3"/>
       <c r="B53" s="4" t="s">
         <v>245</v>
@@ -3015,7 +3016,7 @@
       <c r="E54" s="19"/>
       <c r="F54" s="19"/>
     </row>
-    <row r="55" spans="1:7" ht="30">
+    <row r="55" spans="1:7" ht="28.8">
       <c r="A55" s="3"/>
       <c r="B55" s="8" t="s">
         <v>28</v>
@@ -3030,7 +3031,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="30">
+    <row r="56" spans="1:7" ht="28.8">
       <c r="A56" s="3"/>
       <c r="B56" s="8" t="s">
         <v>29</v>
@@ -3045,7 +3046,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="30">
+    <row r="57" spans="1:7" ht="28.8">
       <c r="A57" s="3"/>
       <c r="B57" s="8" t="s">
         <v>30</v>
@@ -3060,7 +3061,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="75">
+    <row r="58" spans="1:7" ht="57.6">
       <c r="A58" s="3"/>
       <c r="B58" s="8" t="s">
         <v>31</v>
@@ -3085,7 +3086,7 @@
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="1:7" ht="45">
+    <row r="60" spans="1:7" ht="43.2">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
         <v>109</v>
@@ -3100,7 +3101,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60">
+    <row r="61" spans="1:7" ht="57.6">
       <c r="A61" s="3"/>
       <c r="B61" s="4" t="s">
         <v>110</v>
@@ -3115,7 +3116,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="30">
+    <row r="62" spans="1:7" ht="28.8">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
         <v>111</v>
@@ -3130,7 +3131,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="30">
+    <row r="63" spans="1:7" ht="28.8">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
         <v>112</v>
@@ -3148,7 +3149,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="300">
+    <row r="64" spans="1:7" ht="273.60000000000002">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
         <v>113</v>
@@ -3163,7 +3164,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="60">
+    <row r="65" spans="1:6" ht="57.6">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
         <v>114</v>
@@ -3178,7 +3179,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="45">
+    <row r="66" spans="1:6" ht="43.2">
       <c r="A66" s="3"/>
       <c r="B66" s="4" t="s">
         <v>32</v>
@@ -3203,7 +3204,7 @@
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
     </row>
-    <row r="68" spans="1:6" ht="30">
+    <row r="68" spans="1:6" ht="28.8">
       <c r="A68" s="3"/>
       <c r="B68" s="15"/>
       <c r="C68" s="12" t="s">
@@ -3216,7 +3217,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="30">
+    <row r="69" spans="1:6" ht="28.8">
       <c r="A69" s="3"/>
       <c r="B69" s="15"/>
       <c r="C69" s="12" t="s">
@@ -3240,7 +3241,7 @@
       <c r="E71" s="23"/>
       <c r="F71" s="23"/>
     </row>
-    <row r="72" spans="1:6" ht="105">
+    <row r="72" spans="1:6" ht="86.4">
       <c r="B72" s="20" t="s">
         <v>174</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="150">
+    <row r="73" spans="1:6" ht="129.6">
       <c r="B73" s="20" t="s">
         <v>175</v>
       </c>
@@ -3262,7 +3263,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="135">
+    <row r="74" spans="1:6" ht="115.2">
       <c r="B74" s="20" t="s">
         <v>176</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="105">
+    <row r="75" spans="1:6" ht="100.8">
       <c r="B75" s="20" t="s">
         <v>177</v>
       </c>
@@ -3284,7 +3285,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="120">
+    <row r="76" spans="1:6" ht="100.8">
       <c r="B76" s="20" t="s">
         <v>178</v>
       </c>
@@ -3298,7 +3299,7 @@
     <row r="77" spans="1:6">
       <c r="B77" s="2"/>
     </row>
-    <row r="78" spans="1:6" ht="120">
+    <row r="78" spans="1:6" ht="115.2">
       <c r="F78" s="10" t="s">
         <v>200</v>
       </c>
@@ -3310,13 +3311,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96889D9B-A31E-4117-9981-3F4B889EA258}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85491CF7-A128-4D9E-9ABF-9DB116491831}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
-    <col min="3" max="3" width="86.140625" customWidth="1"/>
+    <col min="3" max="3" width="86.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3334,13 +3344,13 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="60">
+    <row r="3" spans="1:3" ht="57.6">
       <c r="A3" s="36"/>
       <c r="C3" s="7" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45">
+    <row r="4" spans="1:3" ht="43.2">
       <c r="A4" s="36"/>
       <c r="C4" s="7" t="s">
         <v>203</v>
@@ -3352,13 +3362,13 @@
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="60">
+    <row r="6" spans="1:3" ht="43.2">
       <c r="A6" s="36"/>
       <c r="C6" s="11" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30">
+    <row r="7" spans="1:3" ht="28.8">
       <c r="A7" s="36"/>
       <c r="C7" s="11" t="s">
         <v>206</v>
@@ -3370,13 +3380,13 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="60">
+    <row r="9" spans="1:3" ht="57.6">
       <c r="A9" s="36"/>
       <c r="C9" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45">
+    <row r="10" spans="1:3" ht="43.2">
       <c r="A10" s="36"/>
       <c r="C10" s="7" t="s">
         <v>209</v>
@@ -3388,7 +3398,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="75">
+    <row r="12" spans="1:3" ht="57.6">
       <c r="A12" s="36"/>
       <c r="C12" s="7" t="s">
         <v>211</v>
@@ -3403,12 +3413,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A4EE27-F9F7-4D2C-A724-37675A5BE28D}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="39.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.109375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3541,7 +3551,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="28.5">
+    <row r="27" spans="1:1" ht="27.6">
       <c r="A27" s="26" t="s">
         <v>266</v>
       </c>
@@ -3652,15 +3662,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44007732-3124-48CF-9F3F-A6232B565BEA}">
   <dimension ref="A1:C124"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="25" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="96.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="27.44140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="96.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3669,11 +3679,11 @@
       </c>
       <c r="B1" s="32"/>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1">
+    <row r="2" spans="1:3" ht="15" thickBot="1">
       <c r="A2" s="32"/>
       <c r="B2" s="32"/>
     </row>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="28" t="s">
         <v>284</v>
       </c>
@@ -3684,7 +3694,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1">
+    <row r="4" spans="1:3" ht="15" thickBot="1">
       <c r="A4" s="34" t="s">
         <v>84</v>
       </c>
@@ -3695,7 +3705,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1">
+    <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="34" t="s">
         <v>85</v>
       </c>
@@ -3706,7 +3716,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" s="34" t="s">
         <v>84</v>
       </c>
@@ -3717,7 +3727,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" s="34" t="s">
         <v>274</v>
       </c>
@@ -3728,7 +3738,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1">
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="34" t="s">
         <v>85</v>
       </c>
@@ -3739,7 +3749,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="29.25" thickBot="1">
+    <row r="9" spans="1:3" ht="28.2" thickBot="1">
       <c r="A9" s="34" t="s">
         <v>13</v>
       </c>
@@ -3750,7 +3760,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
       <c r="A10" s="34" t="s">
         <v>289</v>
       </c>
@@ -3761,7 +3771,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11" s="34" t="s">
         <v>88</v>
       </c>
@@ -3772,7 +3782,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+    <row r="12" spans="1:3" ht="15" thickBot="1">
       <c r="A12" s="34" t="s">
         <v>88</v>
       </c>
@@ -3783,7 +3793,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="34" t="s">
         <v>88</v>
       </c>
@@ -3794,7 +3804,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="34" t="s">
         <v>88</v>
       </c>
@@ -3805,7 +3815,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="34" t="s">
         <v>88</v>
       </c>
@@ -3826,11 +3836,11 @@
       </c>
       <c r="B17" s="32"/>
     </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1">
+    <row r="18" spans="1:3" ht="15" thickBot="1">
       <c r="A18" s="32"/>
       <c r="B18" s="32"/>
     </row>
-    <row r="19" spans="1:3" ht="17.25" thickBot="1">
+    <row r="19" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A19" s="28" t="s">
         <v>284</v>
       </c>
@@ -3841,7 +3851,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1">
+    <row r="20" spans="1:3" ht="15" thickBot="1">
       <c r="A20" s="34" t="s">
         <v>15</v>
       </c>
@@ -3852,7 +3862,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1">
+    <row r="21" spans="1:3" ht="15" thickBot="1">
       <c r="A21" s="34" t="s">
         <v>264</v>
       </c>
@@ -3863,7 +3873,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1">
+    <row r="22" spans="1:3" ht="15" thickBot="1">
       <c r="A22" s="34" t="s">
         <v>15</v>
       </c>
@@ -3874,7 +3884,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+    <row r="23" spans="1:3" ht="15" thickBot="1">
       <c r="A23" s="34" t="s">
         <v>18</v>
       </c>
@@ -3885,7 +3895,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1">
+    <row r="24" spans="1:3" ht="15" thickBot="1">
       <c r="A24" s="34" t="s">
         <v>101</v>
       </c>
@@ -3896,7 +3906,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" thickBot="1">
+    <row r="25" spans="1:3" ht="15" thickBot="1">
       <c r="A25" s="34" t="s">
         <v>18</v>
       </c>
@@ -3907,7 +3917,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="29.25" thickBot="1">
+    <row r="26" spans="1:3" ht="28.2" thickBot="1">
       <c r="A26" s="34" t="s">
         <v>15</v>
       </c>
@@ -3918,7 +3928,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="29.25" thickBot="1">
+    <row r="27" spans="1:3" ht="28.2" thickBot="1">
       <c r="A27" s="34" t="s">
         <v>268</v>
       </c>
@@ -3929,7 +3939,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="29.25" thickBot="1">
+    <row r="28" spans="1:3" ht="28.2" thickBot="1">
       <c r="A28" s="34" t="s">
         <v>15</v>
       </c>
@@ -3940,7 +3950,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+    <row r="29" spans="1:3" ht="15" thickBot="1">
       <c r="A29" s="34" t="s">
         <v>102</v>
       </c>
@@ -3951,7 +3961,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1">
+    <row r="30" spans="1:3" ht="15" thickBot="1">
       <c r="A30" s="34" t="s">
         <v>15</v>
       </c>
@@ -3962,7 +3972,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1">
+    <row r="31" spans="1:3" ht="15" thickBot="1">
       <c r="A31" s="34" t="s">
         <v>100</v>
       </c>
@@ -3973,7 +3983,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1">
+    <row r="32" spans="1:3" ht="15" thickBot="1">
       <c r="A32" s="34" t="s">
         <v>259</v>
       </c>
@@ -3984,7 +3994,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="29.25" thickBot="1">
+    <row r="33" spans="1:3" ht="28.2" thickBot="1">
       <c r="A33" s="34" t="s">
         <v>100</v>
       </c>
@@ -3995,7 +4005,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+    <row r="34" spans="1:3" ht="15" thickBot="1">
       <c r="A34" s="34" t="s">
         <v>15</v>
       </c>
@@ -4010,17 +4020,17 @@
       <c r="A35" s="33"/>
       <c r="B35" s="32"/>
     </row>
-    <row r="36" spans="1:3" ht="30">
+    <row r="36" spans="1:3" ht="28.8">
       <c r="A36" s="31" t="s">
         <v>318</v>
       </c>
       <c r="B36" s="32"/>
     </row>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1">
+    <row r="37" spans="1:3" ht="15" thickBot="1">
       <c r="A37" s="32"/>
       <c r="B37" s="32"/>
     </row>
-    <row r="38" spans="1:3" ht="17.25" thickBot="1">
+    <row r="38" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A38" s="28" t="s">
         <v>284</v>
       </c>
@@ -4031,7 +4041,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" thickBot="1">
+    <row r="39" spans="1:3" ht="15" thickBot="1">
       <c r="A39" s="34" t="s">
         <v>88</v>
       </c>
@@ -4042,7 +4052,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1">
+    <row r="40" spans="1:3" ht="15" thickBot="1">
       <c r="A40" s="34" t="s">
         <v>16</v>
       </c>
@@ -4053,7 +4063,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" thickBot="1">
+    <row r="41" spans="1:3" ht="15" thickBot="1">
       <c r="A41" s="34" t="s">
         <v>88</v>
       </c>
@@ -4064,7 +4074,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" thickBot="1">
+    <row r="42" spans="1:3" ht="15" thickBot="1">
       <c r="A42" s="34" t="s">
         <v>17</v>
       </c>
@@ -4075,7 +4085,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" thickBot="1">
+    <row r="43" spans="1:3" ht="15" thickBot="1">
       <c r="A43" s="34" t="s">
         <v>27</v>
       </c>
@@ -4086,7 +4096,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" thickBot="1">
+    <row r="44" spans="1:3" ht="15" thickBot="1">
       <c r="A44" s="34" t="s">
         <v>17</v>
       </c>
@@ -4097,7 +4107,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" thickBot="1">
+    <row r="45" spans="1:3" ht="15" thickBot="1">
       <c r="A45" s="34" t="s">
         <v>22</v>
       </c>
@@ -4108,7 +4118,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" thickBot="1">
+    <row r="46" spans="1:3" ht="15" thickBot="1">
       <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
@@ -4119,7 +4129,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" thickBot="1">
+    <row r="47" spans="1:3" ht="15" thickBot="1">
       <c r="A47" s="34" t="s">
         <v>17</v>
       </c>
@@ -4130,7 +4140,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="29.25" thickBot="1">
+    <row r="48" spans="1:3" ht="28.2" thickBot="1">
       <c r="A48" s="34" t="s">
         <v>19</v>
       </c>
@@ -4141,7 +4151,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" thickBot="1">
+    <row r="49" spans="1:3" ht="15" thickBot="1">
       <c r="A49" s="34" t="s">
         <v>19</v>
       </c>
@@ -4162,11 +4172,11 @@
       </c>
       <c r="B51" s="32"/>
     </row>
-    <row r="52" spans="1:3" ht="15.75" thickBot="1">
+    <row r="52" spans="1:3" ht="15" thickBot="1">
       <c r="A52" s="32"/>
       <c r="B52" s="32"/>
     </row>
-    <row r="53" spans="1:3" ht="17.25" thickBot="1">
+    <row r="53" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A53" s="28" t="s">
         <v>284</v>
       </c>
@@ -4177,7 +4187,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="29.25" thickBot="1">
+    <row r="54" spans="1:3" ht="28.2" thickBot="1">
       <c r="A54" s="34" t="s">
         <v>267</v>
       </c>
@@ -4188,7 +4198,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="29.25" thickBot="1">
+    <row r="55" spans="1:3" ht="28.2" thickBot="1">
       <c r="A55" s="34" t="s">
         <v>216</v>
       </c>
@@ -4199,7 +4209,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" thickBot="1">
+    <row r="56" spans="1:3" ht="15" thickBot="1">
       <c r="A56" s="34" t="s">
         <v>216</v>
       </c>
@@ -4210,7 +4220,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="29.25" thickBot="1">
+    <row r="57" spans="1:3" ht="28.2" thickBot="1">
       <c r="A57" s="34" t="s">
         <v>267</v>
       </c>
@@ -4221,7 +4231,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="29.25" thickBot="1">
+    <row r="58" spans="1:3" ht="28.2" thickBot="1">
       <c r="A58" s="34" t="s">
         <v>99</v>
       </c>
@@ -4232,7 +4242,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" thickBot="1">
+    <row r="59" spans="1:3" ht="15" thickBot="1">
       <c r="A59" s="34" t="s">
         <v>267</v>
       </c>
@@ -4243,7 +4253,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" thickBot="1">
+    <row r="60" spans="1:3" ht="15" thickBot="1">
       <c r="A60" s="34" t="s">
         <v>98</v>
       </c>
@@ -4254,7 +4264,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" thickBot="1">
+    <row r="61" spans="1:3" ht="15" thickBot="1">
       <c r="A61" s="34" t="s">
         <v>98</v>
       </c>
@@ -4265,7 +4275,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="29.25" thickBot="1">
+    <row r="62" spans="1:3" ht="15" thickBot="1">
       <c r="A62" s="34" t="s">
         <v>267</v>
       </c>
@@ -4276,7 +4286,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="29.25" thickBot="1">
+    <row r="63" spans="1:3" ht="28.2" thickBot="1">
       <c r="A63" s="34" t="s">
         <v>260</v>
       </c>
@@ -4287,7 +4297,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" thickBot="1">
+    <row r="64" spans="1:3" ht="15" thickBot="1">
       <c r="A64" s="34" t="s">
         <v>267</v>
       </c>
@@ -4298,7 +4308,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" thickBot="1">
+    <row r="65" spans="1:3" ht="15" thickBot="1">
       <c r="A65" s="34" t="s">
         <v>93</v>
       </c>
@@ -4309,7 +4319,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" thickBot="1">
+    <row r="66" spans="1:3" ht="15" thickBot="1">
       <c r="A66" s="34" t="s">
         <v>93</v>
       </c>
@@ -4320,7 +4330,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" thickBot="1">
+    <row r="67" spans="1:3" ht="15" thickBot="1">
       <c r="A67" s="34" t="s">
         <v>267</v>
       </c>
@@ -4331,7 +4341,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="57.75" thickBot="1">
+    <row r="68" spans="1:3" ht="55.8" thickBot="1">
       <c r="A68" s="34" t="s">
         <v>242</v>
       </c>
@@ -4342,7 +4352,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" thickBot="1">
+    <row r="69" spans="1:3" ht="15" thickBot="1">
       <c r="A69" s="34" t="s">
         <v>25</v>
       </c>
@@ -4353,7 +4363,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="43.5" thickBot="1">
+    <row r="70" spans="1:3" ht="42" thickBot="1">
       <c r="A70" s="34" t="s">
         <v>348</v>
       </c>
@@ -4364,7 +4374,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" thickBot="1">
+    <row r="71" spans="1:3" ht="15" thickBot="1">
       <c r="A71" s="34" t="s">
         <v>261</v>
       </c>
@@ -4385,11 +4395,11 @@
       </c>
       <c r="B73" s="32"/>
     </row>
-    <row r="74" spans="1:3" ht="15.75" thickBot="1">
+    <row r="74" spans="1:3" ht="15" thickBot="1">
       <c r="A74" s="32"/>
       <c r="B74" s="32"/>
     </row>
-    <row r="75" spans="1:3" ht="17.25" thickBot="1">
+    <row r="75" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A75" s="28" t="s">
         <v>284</v>
       </c>
@@ -4400,7 +4410,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="29.25" thickBot="1">
+    <row r="76" spans="1:3" ht="28.2" thickBot="1">
       <c r="A76" s="34" t="s">
         <v>83</v>
       </c>
@@ -4411,7 +4421,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="29.25" thickBot="1">
+    <row r="77" spans="1:3" ht="28.2" thickBot="1">
       <c r="A77" s="34" t="s">
         <v>82</v>
       </c>
@@ -4422,7 +4432,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="29.25" thickBot="1">
+    <row r="78" spans="1:3" ht="28.2" thickBot="1">
       <c r="A78" s="34" t="s">
         <v>81</v>
       </c>
@@ -4433,7 +4443,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="29.25" thickBot="1">
+    <row r="79" spans="1:3" ht="28.2" thickBot="1">
       <c r="A79" s="34" t="s">
         <v>79</v>
       </c>
@@ -4444,7 +4454,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="29.25" thickBot="1">
+    <row r="80" spans="1:3" ht="28.2" thickBot="1">
       <c r="A80" s="34" t="s">
         <v>262</v>
       </c>
@@ -4455,7 +4465,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="29.25" thickBot="1">
+    <row r="81" spans="1:3" ht="28.2" thickBot="1">
       <c r="A81" s="34" t="s">
         <v>262</v>
       </c>
@@ -4466,7 +4476,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75" thickBot="1">
+    <row r="82" spans="1:3" ht="15" thickBot="1">
       <c r="A82" s="34" t="s">
         <v>250</v>
       </c>
@@ -4477,7 +4487,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" thickBot="1">
+    <row r="83" spans="1:3" ht="15" thickBot="1">
       <c r="A83" s="34" t="s">
         <v>80</v>
       </c>
@@ -4488,7 +4498,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="29.25" thickBot="1">
+    <row r="84" spans="1:3" ht="28.2" thickBot="1">
       <c r="A84" s="34" t="s">
         <v>250</v>
       </c>
@@ -4499,7 +4509,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" thickBot="1">
+    <row r="85" spans="1:3" ht="15" thickBot="1">
       <c r="A85" s="34" t="s">
         <v>250</v>
       </c>
@@ -4510,7 +4520,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="29.25" thickBot="1">
+    <row r="86" spans="1:3" ht="28.2" thickBot="1">
       <c r="A86" s="34" t="s">
         <v>263</v>
       </c>
@@ -4521,7 +4531,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="29.25" thickBot="1">
+    <row r="87" spans="1:3" ht="28.2" thickBot="1">
       <c r="A87" s="34" t="s">
         <v>362</v>
       </c>
@@ -4532,7 +4542,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75" thickBot="1">
+    <row r="88" spans="1:3" ht="15" thickBot="1">
       <c r="A88" s="34" t="s">
         <v>263</v>
       </c>
@@ -4547,17 +4557,17 @@
       <c r="A89" s="33"/>
       <c r="B89" s="32"/>
     </row>
-    <row r="90" spans="1:3" ht="30">
+    <row r="90" spans="1:3" ht="28.8">
       <c r="A90" s="31" t="s">
         <v>366</v>
       </c>
       <c r="B90" s="32"/>
     </row>
-    <row r="91" spans="1:3" ht="15.75" thickBot="1">
+    <row r="91" spans="1:3" ht="15" thickBot="1">
       <c r="A91" s="32"/>
       <c r="B91" s="32"/>
     </row>
-    <row r="92" spans="1:3" ht="17.25" thickBot="1">
+    <row r="92" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A92" s="28" t="s">
         <v>284</v>
       </c>
@@ -4568,7 +4578,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="29.25" thickBot="1">
+    <row r="93" spans="1:3" ht="28.2" thickBot="1">
       <c r="A93" s="34" t="s">
         <v>367</v>
       </c>
@@ -4579,7 +4589,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75" thickBot="1">
+    <row r="94" spans="1:3" ht="15" thickBot="1">
       <c r="A94" s="34" t="s">
         <v>267</v>
       </c>
@@ -4590,7 +4600,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="29.25" thickBot="1">
+    <row r="95" spans="1:3" ht="28.2" thickBot="1">
       <c r="A95" s="34" t="s">
         <v>108</v>
       </c>
@@ -4601,7 +4611,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75" thickBot="1">
+    <row r="96" spans="1:3" ht="15" thickBot="1">
       <c r="A96" s="34" t="s">
         <v>22</v>
       </c>
@@ -4612,7 +4622,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75" thickBot="1">
+    <row r="97" spans="1:3" ht="15" thickBot="1">
       <c r="A97" s="34" t="s">
         <v>102</v>
       </c>
@@ -4633,11 +4643,11 @@
       </c>
       <c r="B99" s="32"/>
     </row>
-    <row r="100" spans="1:3" ht="15.75" thickBot="1">
+    <row r="100" spans="1:3" ht="15" thickBot="1">
       <c r="A100" s="32"/>
       <c r="B100" s="32"/>
     </row>
-    <row r="101" spans="1:3" ht="17.25" thickBot="1">
+    <row r="101" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A101" s="28" t="s">
         <v>284</v>
       </c>
@@ -4648,7 +4658,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75" thickBot="1">
+    <row r="102" spans="1:3" ht="15" thickBot="1">
       <c r="A102" s="34" t="s">
         <v>88</v>
       </c>
@@ -4659,7 +4669,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75" thickBot="1">
+    <row r="103" spans="1:3" ht="15" thickBot="1">
       <c r="A103" s="34" t="s">
         <v>15</v>
       </c>
@@ -4670,7 +4680,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75" thickBot="1">
+    <row r="104" spans="1:3" ht="15" thickBot="1">
       <c r="A104" s="34" t="s">
         <v>17</v>
       </c>
@@ -4681,7 +4691,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="29.25" thickBot="1">
+    <row r="105" spans="1:3" ht="28.2" thickBot="1">
       <c r="A105" s="34" t="s">
         <v>262</v>
       </c>
@@ -4692,7 +4702,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="29.25" thickBot="1">
+    <row r="106" spans="1:3" ht="28.2" thickBot="1">
       <c r="A106" s="34" t="s">
         <v>26</v>
       </c>
@@ -4703,7 +4713,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75" thickBot="1">
+    <row r="107" spans="1:3" ht="15" thickBot="1">
       <c r="A107" s="34" t="s">
         <v>380</v>
       </c>
@@ -4724,11 +4734,11 @@
       </c>
       <c r="B109" s="32"/>
     </row>
-    <row r="110" spans="1:3" ht="15.75" thickBot="1">
+    <row r="110" spans="1:3" ht="15" thickBot="1">
       <c r="A110" s="32"/>
       <c r="B110" s="32"/>
     </row>
-    <row r="111" spans="1:3" ht="17.25" thickBot="1">
+    <row r="111" spans="1:3" ht="17.399999999999999" thickBot="1">
       <c r="A111" s="28" t="s">
         <v>284</v>
       </c>
@@ -4739,7 +4749,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="29.25" thickBot="1">
+    <row r="112" spans="1:3" ht="28.2" thickBot="1">
       <c r="A112" s="34" t="s">
         <v>88</v>
       </c>
@@ -4750,7 +4760,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="29.25" thickBot="1">
+    <row r="113" spans="1:3" ht="28.2" thickBot="1">
       <c r="A113" s="34" t="s">
         <v>15</v>
       </c>
@@ -4761,7 +4771,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="29.25" thickBot="1">
+    <row r="114" spans="1:3" ht="28.2" thickBot="1">
       <c r="A114" s="34" t="s">
         <v>17</v>
       </c>
@@ -4772,7 +4782,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="29.25" thickBot="1">
+    <row r="115" spans="1:3" ht="28.2" thickBot="1">
       <c r="A115" s="34" t="s">
         <v>264</v>
       </c>
@@ -4783,7 +4793,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="29.25" thickBot="1">
+    <row r="116" spans="1:3" ht="28.2" thickBot="1">
       <c r="A116" s="34" t="s">
         <v>267</v>
       </c>
@@ -4794,7 +4804,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="29.25" thickBot="1">
+    <row r="117" spans="1:3" ht="28.2" thickBot="1">
       <c r="A117" s="34" t="s">
         <v>367</v>
       </c>
@@ -4805,7 +4815,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="29.25" thickBot="1">
+    <row r="118" spans="1:3" ht="28.2" thickBot="1">
       <c r="A118" s="34" t="s">
         <v>22</v>
       </c>
@@ -4816,7 +4826,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="29.25" thickBot="1">
+    <row r="119" spans="1:3" ht="28.2" thickBot="1">
       <c r="A119" s="34" t="s">
         <v>268</v>
       </c>
@@ -4827,7 +4837,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75" thickBot="1">
+    <row r="120" spans="1:3" ht="15" thickBot="1">
       <c r="A120" s="34" t="s">
         <v>380</v>
       </c>
@@ -4838,7 +4848,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="29.25" thickBot="1">
+    <row r="121" spans="1:3" ht="28.2" thickBot="1">
       <c r="A121" s="34" t="s">
         <v>380</v>
       </c>
@@ -4849,7 +4859,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="29.25" thickBot="1">
+    <row r="122" spans="1:3" ht="28.2" thickBot="1">
       <c r="A122" s="34" t="s">
         <v>271</v>
       </c>
@@ -4860,7 +4870,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" thickBot="1">
+    <row r="123" spans="1:3" ht="15" thickBot="1">
       <c r="A123" s="34" t="s">
         <v>270</v>
       </c>
@@ -4871,7 +4881,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75" thickBot="1">
+    <row r="124" spans="1:3" ht="15" thickBot="1">
       <c r="A124" s="34" t="s">
         <v>272</v>
       </c>
